--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>95.29187248541665</v>
+        <v>15.48492927888021</v>
       </c>
       <c r="D2" t="n">
-        <v>95.17308970339619</v>
+        <v>15.46562707680188</v>
       </c>
       <c r="E2" t="n">
-        <v>4.16518056654012</v>
+        <v>0.6768418420627695</v>
       </c>
       <c r="F2" t="n">
-        <v>4.172355755938172</v>
+        <v>0.6780078103399531</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>97.23973979564441</v>
+        <v>15.80145771679222</v>
       </c>
       <c r="D3" t="n">
-        <v>97.12816364973214</v>
+        <v>15.78332659308147</v>
       </c>
       <c r="E3" t="n">
-        <v>4.16518056654012</v>
+        <v>0.6768418420627695</v>
       </c>
       <c r="F3" t="n">
-        <v>4.172355755938172</v>
+        <v>0.6780078103399531</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>87.59264980100885</v>
+        <v>14.23380559266394</v>
       </c>
       <c r="D4" t="n">
-        <v>87.46317878366918</v>
+        <v>14.21276655234624</v>
       </c>
       <c r="E4" t="n">
-        <v>4.16518056654012</v>
+        <v>0.6768418420627695</v>
       </c>
       <c r="F4" t="n">
-        <v>4.172355755938172</v>
+        <v>0.6780078103399531</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
